--- a/demo/mc_v12/site_B/04_MCDEMO-B_课题三SSUI_生态_模拟数据_仅供测试演示.xlsx
+++ b/demo/mc_v12/site_B/04_MCDEMO-B_课题三SSUI_生态_模拟数据_仅供测试演示.xlsx
@@ -545,14 +545,10 @@
           <t>场地编号</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>MCDEMO-B</t>
-        </is>
-      </c>
+      <c r="B2" s="3" t="inlineStr"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>必填, 与系统中场地编号一致</t>
+          <t>可留空(以页面所选场地为准); 填写时须与系统中场地编号一致</t>
         </is>
       </c>
     </row>

--- a/demo/mc_v12/site_B/04_MCDEMO-B_课题三SSUI_生态_模拟数据_仅供测试演示.xlsx
+++ b/demo/mc_v12/site_B/04_MCDEMO-B_课题三SSUI_生态_模拟数据_仅供测试演示.xlsx
@@ -654,7 +654,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>mc_demo_v12.0 seed=20261009 场景B</t>
+          <t>mc_demo_v12.2 seed=20261009 场景B</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
@@ -758,7 +758,7 @@
       <c r="E2" s="3" t="n"/>
       <c r="F2" s="3" t="n"/>
       <c r="G2" s="3" t="n">
-        <v>0.6276</v>
+        <v>0.439</v>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="n"/>
       <c r="G3" s="3" t="n">
-        <v>0.2821</v>
+        <v>0.2917</v>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
       <c r="E4" s="3" t="n"/>
       <c r="F4" s="3" t="n"/>
       <c r="G4" s="3" t="n">
-        <v>0.3502</v>
+        <v>0.253</v>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="n">
-        <v>0.1721</v>
+        <v>0.3402</v>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
@@ -878,7 +878,7 @@
       <c r="E6" s="3" t="n"/>
       <c r="F6" s="3" t="n"/>
       <c r="G6" s="3" t="n">
-        <v>0.529</v>
+        <v>0.4121</v>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
       <c r="E7" s="3" t="n"/>
       <c r="F7" s="3" t="n"/>
       <c r="G7" s="3" t="n">
-        <v>0.3091</v>
+        <v>0.3117</v>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
       <c r="E8" s="3" t="n"/>
       <c r="F8" s="3" t="n"/>
       <c r="G8" s="3" t="n">
-        <v>0.2188</v>
+        <v>0.3248</v>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
@@ -968,7 +968,7 @@
       <c r="E9" s="3" t="n"/>
       <c r="F9" s="3" t="n"/>
       <c r="G9" s="3" t="n">
-        <v>0.4053</v>
+        <v>0.1208</v>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
       <c r="E10" s="3" t="n"/>
       <c r="F10" s="3" t="n"/>
       <c r="G10" s="3" t="n">
-        <v>0.244</v>
+        <v>0.1999</v>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
       <c r="E11" s="3" t="n"/>
       <c r="F11" s="3" t="n"/>
       <c r="G11" s="3" t="n">
-        <v>0.1998</v>
+        <v>0.4191</v>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
       <c r="E12" s="3" t="n"/>
       <c r="F12" s="3" t="n"/>
       <c r="G12" s="3" t="n">
-        <v>0.3264</v>
+        <v>0.2548</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
       <c r="E13" s="3" t="n"/>
       <c r="F13" s="3" t="n"/>
       <c r="G13" s="3" t="n">
-        <v>0.3351</v>
+        <v>0.3873</v>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
       <c r="E14" s="3" t="n"/>
       <c r="F14" s="3" t="n"/>
       <c r="G14" s="3" t="n">
-        <v>0.1814</v>
+        <v>0.3423</v>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
@@ -1148,7 +1148,7 @@
       <c r="E15" s="3" t="n"/>
       <c r="F15" s="3" t="n"/>
       <c r="G15" s="3" t="n">
-        <v>0.1407</v>
+        <v>0.447</v>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
       <c r="E16" s="3" t="n"/>
       <c r="F16" s="3" t="n"/>
       <c r="G16" s="3" t="n">
-        <v>0.4113</v>
+        <v>0.2072</v>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
       <c r="E17" s="3" t="n"/>
       <c r="F17" s="3" t="n"/>
       <c r="G17" s="3" t="n">
-        <v>0.2432</v>
+        <v>0.3613</v>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
       <c r="E18" s="3" t="n"/>
       <c r="F18" s="3" t="n"/>
       <c r="G18" s="3" t="n">
-        <v>0.3009</v>
+        <v>0.4456</v>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
       <c r="E19" s="3" t="n"/>
       <c r="F19" s="3" t="n"/>
       <c r="G19" s="3" t="n">
-        <v>0.4528</v>
+        <v>0.3054</v>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
       <c r="E20" s="3" t="n"/>
       <c r="F20" s="3" t="n"/>
       <c r="G20" s="3" t="n">
-        <v>0.2399</v>
+        <v>0.383</v>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       <c r="E21" s="3" t="n"/>
       <c r="F21" s="3" t="n"/>
       <c r="G21" s="3" t="n">
-        <v>0.2275</v>
+        <v>0.3757</v>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
       <c r="E22" s="3" t="n"/>
       <c r="F22" s="3" t="n"/>
       <c r="G22" s="3" t="n">
-        <v>0.1592</v>
+        <v>0.397</v>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       <c r="E23" s="3" t="n"/>
       <c r="F23" s="3" t="n"/>
       <c r="G23" s="3" t="n">
-        <v>0.1785</v>
+        <v>0.3128</v>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       <c r="E24" s="3" t="n"/>
       <c r="F24" s="3" t="n"/>
       <c r="G24" s="3" t="n">
-        <v>0.3935</v>
+        <v>0.2907</v>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
       <c r="E25" s="3" t="n"/>
       <c r="F25" s="3" t="n"/>
       <c r="G25" s="3" t="n">
-        <v>0.363</v>
+        <v>0.2319</v>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
       <c r="E26" s="3" t="n"/>
       <c r="F26" s="3" t="n"/>
       <c r="G26" s="3" t="n">
-        <v>0.2358</v>
+        <v>0.4816</v>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
